--- a/public/data/classes.xlsx
+++ b/public/data/classes.xlsx
@@ -1,29 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02dd4aa8eaaca434/Desktop/robotix/public/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_5D6971D6FFF13905CAEC43E89FD61D851F41BA21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC0CABDC-F497-4B90-8BF7-713FA0447912}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Classes" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Classes" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Classes!$A$1:$L$11</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -72,6 +55,9 @@
     <t>Robotics (General)</t>
   </si>
   <si>
+    <t>Ages 5-15</t>
+  </si>
+  <si>
     <t>Hands-on building, sensors, and engineering fundamentals for young makers.</t>
   </si>
   <si>
@@ -144,42 +130,48 @@
     <t>Math</t>
   </si>
   <si>
+    <t>K-8</t>
+  </si>
+  <si>
+    <t>Skill-building practice that grows academic confidence, matched to each student's level.</t>
+  </si>
+  <si>
+    <t>$49 one-time (per subject)</t>
+  </si>
+  <si>
+    <t>Price is per subject</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ages 9+ &amp; for Adults </t>
+  </si>
+  <si>
+    <t>Beginner-friendly Python programming that turns logical thinking into real, working code.</t>
+  </si>
+  <si>
+    <t>No free trial</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>3D Printing</t>
+  </si>
+  <si>
     <t>All ages</t>
   </si>
   <si>
-    <t>Skill-building practice that grows academic confidence, matched to each student's level.</t>
-  </si>
-  <si>
-    <t>$49 one-time (per subject)</t>
-  </si>
-  <si>
-    <t>Price is per subject</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Coding</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>Beginner-friendly Python programming that turns logical thinking into real, working code.</t>
-  </si>
-  <si>
-    <t>No free trial</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>3D Printing</t>
-  </si>
-  <si>
     <t>Design and print 3D creations. Program details coming soon.</t>
   </si>
   <si>
@@ -198,52 +190,46 @@
     <t>After School Pick Up</t>
   </si>
   <si>
-    <t>We pick your child up from select schools and help with homework until you arrive.</t>
-  </si>
-  <si>
-    <t>$100</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>Daily (school days)</t>
-  </si>
-  <si>
-    <t>Includes homework help only; check school list for eligible schools</t>
-  </si>
-  <si>
-    <t>Ages 5-15</t>
-  </si>
-  <si>
-    <t>K-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ages 9+ &amp; for Adults </t>
-  </si>
-  <si>
-    <t>As Listed
+    <t xml:space="preserve">As Listed
 CMS- Middle &amp; High School
 Poplar Hill Elementary &amp; More</t>
+  </si>
+  <si>
+    <t>We pick your child up from select schools and help with homework until you arrive.</t>
+  </si>
+  <si>
+    <t>$75</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>Daily (school days)</t>
+  </si>
+  <si>
+    <t>Includes homework help only; check school list for eligible schools</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -256,7 +242,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -277,7 +262,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -286,74 +271,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFD9EAF7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -370,10 +287,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -411,156 +328,300 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="3" max="3" width="19.857142857142858" customWidth="1"/>
+    <col min="4" max="4" width="42.142857142857146" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
+    <col min="12" max="12" width="42.142857142857146" customWidth="1"/>
+    <col min="13" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -606,371 +667,371 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>41</v>
+      <c r="K8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
+    <row r="9" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="101.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A1:L11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>